--- a/期中考.xlsx
+++ b/期中考.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/che/Library/CloudStorage/Dropbox/che_workspace/teaching/collage/precalculus/114_1_龍華科大/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBA851D-61A8-C545-B577-EC1A4300F45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009ABF0A-D0A1-2344-AED8-4ECBD0282746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21620" xr2:uid="{07F953FE-9310-774E-A3E4-AA961A242C55}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21600" xr2:uid="{07F953FE-9310-774E-A3E4-AA961A242C55}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2031,6 +2031,9 @@
       <c r="D69" s="1" t="s">
         <v>157</v>
       </c>
+      <c r="E69">
+        <v>113</v>
+      </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1" t="s">

--- a/期中考.xlsx
+++ b/期中考.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/che/Library/CloudStorage/Dropbox/che_workspace/teaching/collage/precalculus/114_1_龍華科大/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009ABF0A-D0A1-2344-AED8-4ECBD0282746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040B3B7E-9E56-0D46-BAB9-6252C59CE9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21600" xr2:uid="{07F953FE-9310-774E-A3E4-AA961A242C55}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="164">
   <si>
     <t>D1104181019</t>
   </si>
@@ -528,6 +528,10 @@
   </si>
   <si>
     <t>分數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最後輸出</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -914,14 +918,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFF9832-4926-3E44-8F80-FAF764F9A221}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -935,7 +939,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -949,8 +953,11 @@
       <c r="G2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,8 +970,19 @@
       <c r="D3" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H5" si="0">IF(
+    AND(G3="",E3=""),
+    "",
+    IFERROR(
+        IF(G3="", IF(E3&gt;100,100,E3), IF(G3&gt;100,100,G3)),
+        IF(E3&gt;100,100,E3)
+    )
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -980,8 +998,16 @@
       <c r="E4">
         <v>115</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="G4">
+        <f t="shared" ref="G4:G5" si="1">IF(AND(E4="",F4=""),"",E4+F4)</f>
+        <v>115</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -997,8 +1023,16 @@
       <c r="E5">
         <v>103</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1045,23 @@
       <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="G6" t="str">
+        <f>IF(AND(E6="",F6=""),"",E6+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(
+    AND(G6="",E6=""),
+    "",
+    IFERROR(
+        IF(G6="", IF(E6&gt;100,100,E6), IF(G6&gt;100,100,G6)),
+        IF(E6&gt;100,100,E6)
+    )
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1025,8 +1074,26 @@
       <c r="D7" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G70" si="2">IF(AND(E7="",F7=""),"",E7+F7)</f>
+        <v>55</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7:H70" si="3">IF(
+    AND(G7="",E7=""),
+    "",
+    IFERROR(
+        IF(G7="", IF(E7&gt;100,100,E7), IF(G7&gt;100,100,G7)),
+        IF(E7&gt;100,100,E7)
+    )
+)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1046,10 +1113,15 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1065,8 +1137,16 @@
       <c r="E9">
         <v>105</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,8 +1162,16 @@
       <c r="E10">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1099,8 +1187,16 @@
       <c r="E11">
         <v>114</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>114</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1113,11 +1209,22 @@
       <c r="D12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1137,10 +1244,15 @@
         <v>10</v>
       </c>
       <c r="G13">
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1160,10 +1272,15 @@
         <v>10</v>
       </c>
       <c r="G14">
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1179,8 +1296,16 @@
       <c r="E15">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1196,8 +1321,16 @@
       <c r="E16">
         <v>112</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>112</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1210,8 +1343,16 @@
       <c r="D17" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="G17" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -1227,8 +1368,16 @@
       <c r="E18">
         <v>117</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
@@ -1244,8 +1393,16 @@
       <c r="E19">
         <v>120</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1261,8 +1418,19 @@
       <c r="E20">
         <v>88</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -1278,8 +1446,16 @@
       <c r="E21">
         <v>120</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1295,8 +1471,16 @@
       <c r="E22">
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1312,8 +1496,16 @@
       <c r="E23">
         <v>110</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -1329,8 +1521,16 @@
       <c r="E24">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>101</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
@@ -1343,8 +1543,19 @@
       <c r="D25" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25">
+        <v>120</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -1360,8 +1571,16 @@
       <c r="E26">
         <v>114</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="G26">
+        <f t="shared" si="2"/>
+        <v>114</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,8 +1596,16 @@
       <c r="E27">
         <v>120</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="G27">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
@@ -1394,8 +1621,16 @@
       <c r="E28">
         <v>85</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="G28">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -1411,8 +1646,16 @@
       <c r="E29">
         <v>120</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="G29">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
@@ -1428,8 +1671,16 @@
       <c r="E30">
         <v>120</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="G30">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
@@ -1445,8 +1696,16 @@
       <c r="E31">
         <v>107</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="G31">
+        <f t="shared" si="2"/>
+        <v>107</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
@@ -1462,8 +1721,16 @@
       <c r="E32">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="G32">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
@@ -1479,8 +1746,16 @@
       <c r="E33">
         <v>120</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="G33">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
@@ -1496,8 +1771,16 @@
       <c r="E34">
         <v>97</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="G34">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="3"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -1510,8 +1793,19 @@
       <c r="D35" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="E35">
+        <v>27</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
@@ -1524,8 +1818,22 @@
       <c r="D36" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
@@ -1541,8 +1849,16 @@
       <c r="E37">
         <v>95</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="G37">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
@@ -1558,8 +1874,16 @@
       <c r="E38">
         <v>120</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="G38">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -1575,8 +1899,16 @@
       <c r="E39">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="G39">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
@@ -1589,8 +1921,22 @@
       <c r="D40" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="E40">
+        <v>96</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
@@ -1606,8 +1952,16 @@
       <c r="E41">
         <v>120</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="G41">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
@@ -1623,8 +1977,16 @@
       <c r="E42">
         <v>115</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="G42">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
@@ -1640,8 +2002,16 @@
       <c r="E43">
         <v>90</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="G43">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
@@ -1654,8 +2024,16 @@
       <c r="D44" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="G44" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
         <v>42</v>
       </c>
@@ -1671,8 +2049,16 @@
       <c r="E45">
         <v>89</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="G45">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
@@ -1685,8 +2071,22 @@
       <c r="D46" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="E46">
+        <v>60</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
         <v>44</v>
       </c>
@@ -1702,8 +2102,16 @@
       <c r="E47">
         <v>120</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="G47">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
         <v>45</v>
       </c>
@@ -1716,8 +2124,16 @@
       <c r="D48" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="G48" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
         <v>46</v>
       </c>
@@ -1730,8 +2146,19 @@
       <c r="D49" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="E49">
+        <v>115</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
         <v>47</v>
       </c>
@@ -1744,8 +2171,16 @@
       <c r="D50" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="G50" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
         <v>48</v>
       </c>
@@ -1761,8 +2196,16 @@
       <c r="E51">
         <v>95</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="G51">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
         <v>49</v>
       </c>
@@ -1778,8 +2221,16 @@
       <c r="E52">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="G52">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
         <v>50</v>
       </c>
@@ -1792,8 +2243,16 @@
       <c r="D53" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="G53" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
         <v>51</v>
       </c>
@@ -1809,8 +2268,16 @@
       <c r="E54">
         <v>95</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="G54">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
         <v>52</v>
       </c>
@@ -1823,8 +2290,16 @@
       <c r="D55" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="G55" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
         <v>53</v>
       </c>
@@ -1837,8 +2312,19 @@
       <c r="D56" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="E56">
+        <v>120</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
         <v>54</v>
       </c>
@@ -1854,8 +2340,16 @@
       <c r="E57">
         <v>94</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="G57">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="3"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
         <v>55</v>
       </c>
@@ -1869,10 +2363,21 @@
         <v>106</v>
       </c>
       <c r="E58">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="3"/>
+        <v>88</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
         <v>56</v>
       </c>
@@ -1885,8 +2390,22 @@
       <c r="D59" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="E59">
+        <v>85</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1" t="s">
         <v>57</v>
       </c>
@@ -1899,8 +2418,22 @@
       <c r="D60" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="E60">
+        <v>90</v>
+      </c>
+      <c r="F60">
+        <v>10</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1" t="s">
         <v>58</v>
       </c>
@@ -1913,8 +2446,16 @@
       <c r="D61" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="G61" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1" t="s">
         <v>59</v>
       </c>
@@ -1930,8 +2471,16 @@
       <c r="E62">
         <v>87</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="G62">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="3"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
         <v>60</v>
       </c>
@@ -1944,8 +2493,16 @@
       <c r="D63" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="G63" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1" t="s">
         <v>61</v>
       </c>
@@ -1958,8 +2515,22 @@
       <c r="D64" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="E64">
+        <v>92</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
         <v>62</v>
       </c>
@@ -1975,8 +2546,16 @@
       <c r="E65">
         <v>102</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="G65">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>63</v>
       </c>
@@ -1989,8 +2568,16 @@
       <c r="D66" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="G66" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
         <v>64</v>
       </c>
@@ -2003,8 +2590,16 @@
       <c r="D67" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="G67" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
         <v>65</v>
       </c>
@@ -2017,8 +2612,22 @@
       <c r="D68" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="E68">
+        <v>97</v>
+      </c>
+      <c r="F68">
+        <v>10</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="2"/>
+        <v>107</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>66</v>
       </c>
@@ -2034,8 +2643,16 @@
       <c r="E69">
         <v>113</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="G69">
+        <f t="shared" si="2"/>
+        <v>113</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>67</v>
       </c>
@@ -2050,6 +2667,14 @@
       </c>
       <c r="E70">
         <v>102</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
